--- a/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="79">
   <si>
     <t>Dự án</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Tên bộ phận</t>
   </si>
   <si>
-    <t>Cọc khoan nhồi - Trụ HN P479</t>
+    <t>Cọc khoan nhồi - Trụ HN           P479</t>
   </si>
   <si>
     <t>Số hiệu cọc</t>
@@ -253,9 +253,6 @@
   <si>
     <t xml:space="preserve">16h35'
 04/03/2026</t>
-  </si>
-  <si>
-    <t>ẢNH BIÊN BẢN GỐC</t>
   </si>
   <si>
     <t>STT</t>
@@ -289,7 +286,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -347,12 +344,6 @@
     <font>
       <color rgb="FF365314"/>
       <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -430,7 +421,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -485,21 +476,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF1A3A6B"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF1A3A6B"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF1A3A6B"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF1A3A6B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
@@ -517,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -591,13 +567,10 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -615,50 +588,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="8096250" cy="10477500"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -983,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2111,83 +2040,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="25"/>
-    </row>
-    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
@@ -2196,11 +2050,9 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2219,31 +2071,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2421,31 +2273,31 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="27">
+      <c r="A8" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="26">
         <v>27</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="26">
         <v>-6.72</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="26">
         <v>-63</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="26">
         <v>13.02</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="26">
         <v>56.28</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="26">
         <v>4.32</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -29,7 +29,7 @@
     <t>Tên bộ phận</t>
   </si>
   <si>
-    <t>Cọc khoan nhồi - Trụ HN           P479</t>
+    <t>Cọc khoan nhồi - Trụ HN  @@@P479</t>
   </si>
   <si>
     <t>Số hiệu cọc</t>

--- a/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D2000</t>
+    <t>D1500</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="80">
   <si>
     <t>Dự án</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1500</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -253,6 +253,9 @@
   <si>
     <t xml:space="preserve">16h35'
 04/03/2026</t>
+  </si>
+  <si>
+    <t>ẢNH BIÊN BẢN GỐC</t>
   </si>
   <si>
     <t>STT</t>
@@ -286,7 +289,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -344,6 +347,12 @@
     <font>
       <color rgb="FF365314"/>
       <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -421,7 +430,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -476,6 +485,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF1A3A6B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1A3A6B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1A3A6B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1A3A6B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
@@ -493,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -567,10 +591,13 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -588,6 +615,50 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="8096250" cy="10477500"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -912,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2040,8 +2111,83 @@
         <v>30</v>
       </c>
     </row>
+    <row r="40" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
@@ -2050,9 +2196,11 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2071,31 +2219,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2273,31 +2421,31 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="26">
+      <c r="A8" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="27">
         <v>27</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <v>-6.72</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <v>-63</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <v>13.02</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <v>56.28</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <v>4.32</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1200</t>
+    <t>D1500</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1500</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/hum8wv_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="81">
   <si>
     <t>Dự án</t>
   </si>
@@ -117,6 +117,9 @@
   <si>
     <t xml:space="preserve">11h26'
 03/03/2026</t>
+  </si>
+  <si>
+    <t>-100.88</t>
   </si>
   <si>
     <t xml:space="preserve">12h55'
@@ -401,12 +404,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -552,17 +555,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1220,17 +1223,17 @@
       <c r="F12" s="9">
         <v>-8.81</v>
       </c>
-      <c r="G12" s="9">
-        <v>-10.88</v>
+      <c r="G12" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="H12" s="9">
         <v>0.48</v>
       </c>
       <c r="I12" s="9">
-        <v>2.07</v>
-      </c>
-      <c r="J12" s="8">
-        <v>4.28</v>
+        <v>92.07</v>
+      </c>
+      <c r="J12" s="12">
+        <v>190.49</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1247,10 +1250,10 @@
         <v>32</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="9">
         <v>-10.88</v>
@@ -1282,10 +1285,10 @@
         <v>32</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" s="9">
         <v>-12.94</v>
@@ -1307,300 +1310,300 @@
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="12">
+      <c r="E15" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="13">
         <v>-14.1</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <v>-16.14</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <v>0.43</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <v>2.04</v>
       </c>
       <c r="J15" s="8">
         <v>4.71</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="13" t="s">
+      <c r="A16" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="B16" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="12">
+      <c r="E16" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="13">
         <v>-16.14</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <v>-18.22</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <v>0.35</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <v>2.08</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="12">
         <v>5.94</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="14" t="s">
+      <c r="B17" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="12">
+      <c r="E17" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="13">
         <v>-18.22</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="13">
         <v>-20.43</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <v>0.32</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <v>2.21</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="12">
         <v>6.98</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="13" t="s">
+      <c r="A18" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="14" t="s">
+      <c r="B18" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="12">
+      <c r="E18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="13">
         <v>-20.43</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <v>-22.56</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <v>0.27</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <v>2.13</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="12">
         <v>7.99</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="A19" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="14" t="s">
+      <c r="B19" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="12">
+      <c r="E19" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="13">
         <v>-22.56</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="13">
         <v>-24.67</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <v>0.4</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="13">
         <v>2.11</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="12">
         <v>5.28</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="K19" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="13" t="s">
+      <c r="A20" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="B20" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="12">
+      <c r="E20" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="13">
         <v>-24.67</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="13">
         <v>-26.73</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <v>0.27</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <v>2.06</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="12">
         <v>7.72</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K20" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="B21" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="12">
+      <c r="E21" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="13">
         <v>-26.73</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="13">
         <v>-28.87</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="13">
         <v>0.27</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="13">
         <v>2.14</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="12">
         <v>8.03</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="K21" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="14" t="s">
+      <c r="B22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="12">
+      <c r="E22" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="13">
         <v>-28.87</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="13">
         <v>-31.01</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="13">
         <v>0.28</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="13">
         <v>2.14</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="12">
         <v>7.55</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="K22" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>46</v>
-      </c>
       <c r="E23" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" s="16">
         <v>-31.01</v>
@@ -1614,7 +1617,7 @@
       <c r="I23" s="16">
         <v>2.11</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="12">
         <v>5.27</v>
       </c>
       <c r="K23" s="17" t="s">
@@ -1623,19 +1626,19 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>49</v>
-      </c>
       <c r="E24" s="21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F24" s="19">
         <v>-33.12</v>
@@ -1649,7 +1652,7 @@
       <c r="I24" s="19">
         <v>1.96</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="12">
         <v>5.11</v>
       </c>
       <c r="K24" s="20" t="s">
@@ -1658,19 +1661,19 @@
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F25" s="19">
         <v>-35.08</v>
@@ -1693,19 +1696,19 @@
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F26" s="22">
         <v>-37.06</v>
@@ -1728,19 +1731,19 @@
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F27" s="22">
         <v>-39.12</v>
@@ -1763,19 +1766,19 @@
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F28" s="22">
         <v>-40.98</v>
@@ -1798,19 +1801,19 @@
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F29" s="22">
         <v>-43.1</v>
@@ -1833,19 +1836,19 @@
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" s="22">
         <v>-45.07</v>
@@ -1859,7 +1862,7 @@
       <c r="I30" s="22">
         <v>4.04</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="12">
         <v>6.55</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -1868,19 +1871,19 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F31" s="22">
         <v>-49.11</v>
@@ -1903,19 +1906,19 @@
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F32" s="22">
         <v>-51.23</v>
@@ -1929,7 +1932,7 @@
       <c r="I32" s="22">
         <v>1.97</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="12">
         <v>6.57</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -1938,19 +1941,19 @@
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F33" s="22">
         <v>-53.2</v>
@@ -1973,19 +1976,19 @@
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F34" s="22">
         <v>-55.19</v>
@@ -2008,19 +2011,19 @@
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B35" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F35" s="22">
         <v>-57.22</v>
@@ -2043,19 +2046,19 @@
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B36" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F36" s="22">
         <v>-59.35</v>
@@ -2078,19 +2081,19 @@
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B37" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F37" s="22">
         <v>-61.2</v>
@@ -2113,7 +2116,7 @@
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B40" s="25"/>
       <c r="C40" s="25"/>
@@ -2219,31 +2222,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2298,38 +2301,38 @@
         <v>1.53</v>
       </c>
       <c r="H3" s="9">
-        <v>5.29</v>
-      </c>
-      <c r="I3" s="8">
-        <v>3.45</v>
+        <v>95.29</v>
+      </c>
+      <c r="I3" s="12">
+        <v>62.15</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="B4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="13">
         <v>8</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>-14.1</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <v>-31.01</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="13">
         <v>2.58</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="13">
         <v>16.91</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="12">
         <v>6.55</v>
       </c>
     </row>
@@ -2341,7 +2344,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -2358,7 +2361,7 @@
       <c r="H5" s="16">
         <v>2.11</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="12">
         <v>5.27</v>
       </c>
     </row>
@@ -2370,7 +2373,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" s="19">
         <v>2</v>
@@ -2399,7 +2402,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" s="22">
         <v>12</v>
@@ -2422,7 +2425,7 @@
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>30</v>
@@ -2443,10 +2446,10 @@
         <v>13.02</v>
       </c>
       <c r="H8" s="27">
-        <v>56.28</v>
+        <v>146.28</v>
       </c>
       <c r="I8" s="27">
-        <v>4.32</v>
+        <v>11.24</v>
       </c>
     </row>
   </sheetData>
